--- a/output/pdf_financials_xlsx/SOBO.xlsx
+++ b/output/pdf_financials_xlsx/SOBO.xlsx
@@ -15125,7 +15125,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -17715,7 +17715,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E287" s="5" t="n">

--- a/output/pdf_financials_xlsx/SOBO.xlsx
+++ b/output/pdf_financials_xlsx/SOBO.xlsx
@@ -2299,22 +2299,22 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>3057</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>4183</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>4330</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.001229</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.001062</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.000754</v>
       </c>
     </row>
     <row r="65">
@@ -2419,22 +2419,22 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>3057</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>4183</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>4330</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.001229</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>0.001062</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>0.000754</v>
       </c>
     </row>
     <row r="69">
@@ -2629,22 +2629,22 @@
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>10015</v>
+        <v>6958</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>11721</v>
+        <v>7538</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>15009</v>
+        <v>10679</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.002075</v>
+        <v>0.000846</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.001761</v>
+        <v>0.000699</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.001341</v>
+        <v>0.000587</v>
       </c>
     </row>
     <row r="76">
@@ -4417,7 +4417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K288"/>
+  <dimension ref="A1:K290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6676,14 +6676,10 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Critical Audit Matters</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Coastal GasLink LP was $3.3 billion as of December</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -6697,11 +6693,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G45" s="5" t="n">
-        <v>2022</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>31</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -6725,17 +6725,17 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>personnel</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>changes in circumstances indicate that the Columbia reporting unit goodwill might be impaired. This qualitative assessment was performed as of December</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Liabilities and Shareholder's Equity</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -6746,11 +6746,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G46" s="5" t="n">
-        <v>2022</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>31</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -6776,12 +6780,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Critical Audit Matters</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Loans receivable from affiliates (Note 12)</t>
+          <t>Coastal GasLink LP was $3.3 billion as of December</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -6796,12 +6800,10 @@
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1217</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2022</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>31</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -6827,32 +6829,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>personnel</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inventories</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
+          <t>changes in circumstances indicate that the Columbia reporting unit goodwill might be impaired. This qualitative assessment was performed as of December</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="5" t="n">
-        <v>629</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>724</v>
+        <v>2022</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>936</v>
+        <v>31</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -6883,14 +6883,10 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Other current assets (Note 8)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>OtherCurrentAssets</t>
-        </is>
-      </c>
+          <t>Loans receivable from affiliates (Note 12)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -6902,10 +6898,12 @@
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1717</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>2152</v>
+        <v>1217</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -6936,12 +6934,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Current Assets total</t>
+          <t>Inventories</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6950,13 +6948,13 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>5201</v>
+        <v>629</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>7423</v>
+        <v>724</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>7332</v>
+        <v>936</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -6987,12 +6985,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plant, Property and Equipment (Note 9)</t>
+          <t>Other current assets (Note 8)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NetPPE</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7006,10 +7004,10 @@
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>70182</v>
+        <v>1717</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>75940</v>
+        <v>2152</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -7040,27 +7038,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Net Investment in Leases (Note 10)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Current Assets total</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F52" s="5" t="n">
+        <v>5201</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>7423</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>1895</v>
+        <v>7332</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -7091,12 +7089,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Equity Investments (Note 11)</t>
+          <t>Plant, Property and Equipment (Note 9)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EquityInvestments</t>
+          <t>NetPPE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -7110,10 +7108,10 @@
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>8441</v>
+        <v>70182</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>9535</v>
+        <v>75940</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -7144,7 +7142,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Long-Term Loans Receivable from Affiliate (Notes 7 and 12)</t>
+          <t>Net Investment in Leases (Note 10)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -7158,13 +7156,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n">
-        <v>238</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>1895</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -7195,12 +7193,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Restricted Investments</t>
+          <t>Equity Investments (Note 11)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>RestrictedInvestments</t>
+          <t>EquityInvestments</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7208,14 +7206,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>1898</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2182</v>
+        <v>8441</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>2108</v>
+        <v>9535</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -7246,14 +7246,10 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Regulatory Assets (Note 13)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>RegulatoryAssets</t>
-        </is>
-      </c>
+          <t>Long-Term Loans Receivable from Affiliate (Notes 7 and 12)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -7265,10 +7261,12 @@
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>1767</v>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>1910</v>
+        <v>238</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -7299,12 +7297,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Goodwill (Note 14)</t>
+          <t>Restricted Investments</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>RestrictedInvestments</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7312,16 +7310,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F57" s="5" t="n">
+        <v>1898</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>12582</v>
+        <v>2182</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>12843</v>
+        <v>2108</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -7352,12 +7348,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Other Long-Term Assets (Note 15)</t>
+          <t>Regulatory Assets (Note 13)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OtherNonCurrentAssets</t>
+          <t>RegulatoryAssets</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7371,10 +7367,10 @@
         </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1403</v>
+        <v>1767</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>2785</v>
+        <v>1910</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -7400,15 +7396,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Notes payable (Note 16)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Goodwill (Note 14)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>5166</v>
+        <v>12582</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>6262</v>
+        <v>12843</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -7449,15 +7449,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Accounts payable and other (Note 17)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Other Long-Term Assets (Note 15)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>OtherNonCurrentAssets</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -7469,10 +7473,10 @@
         </is>
       </c>
       <c r="G60" s="5" t="n">
-        <v>5099</v>
+        <v>1403</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>7149</v>
+        <v>2785</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -7503,27 +7507,25 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dividends payable</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>DividendsPayable</t>
-        </is>
-      </c>
+          <t>Notes payable (Note 16)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F61" s="5" t="n">
-        <v>795</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>879</v>
+        <v>5166</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>930</v>
+        <v>6262</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -7554,7 +7556,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Accrued interest</t>
+          <t>Accounts payable and other (Note 17)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -7563,14 +7565,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F62" s="5" t="n">
-        <v>595</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G62" s="5" t="n">
-        <v>577</v>
+        <v>5099</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>668</v>
+        <v>7149</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -7601,12 +7605,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Current portion of long-term debt (Note 20)</t>
+          <t>Dividends payable</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CurrentDebt</t>
+          <t>DividendsPayable</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7614,16 +7618,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F63" s="5" t="n">
+        <v>795</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1320</v>
+        <v>879</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>1898</v>
+        <v>930</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -7654,27 +7656,23 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Current Liabilities total</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>CurrentLiabilities</t>
-        </is>
-      </c>
+          <t>Accrued interest</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>11987</v>
+        <v>595</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>13041</v>
+        <v>577</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>16907</v>
+        <v>668</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -7705,12 +7703,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Regulatory Liabilities (Note 13)</t>
+          <t>Current portion of long-term debt (Note 20)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RegulatoryLiabilities</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7724,10 +7722,10 @@
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>4300</v>
+        <v>1320</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>4520</v>
+        <v>1898</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -7758,25 +7756,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Other Long-Term Liabilities (Note 18)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Current Liabilities total</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CurrentLiabilities</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F66" s="5" t="n">
+        <v>11987</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>1059</v>
+        <v>13041</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>1017</v>
+        <v>16907</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -7807,10 +7807,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Deferred Income Tax Liabilities (Note 19)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Regulatory Liabilities (Note 13)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>RegulatoryLiabilities</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -7822,10 +7826,10 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>6142</v>
+        <v>4300</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>7648</v>
+        <v>4520</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -7856,14 +7860,10 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Long-Term Debt (Note 20)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>LongTermDebt</t>
-        </is>
-      </c>
+          <t>Other Long-Term Liabilities (Note 18)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="G68" s="5" t="n">
-        <v>37341</v>
+        <v>1059</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>39645</v>
+        <v>1017</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Junior Subordinated Notes (Note 21)</t>
+          <t>Deferred Income Tax Liabilities (Note 19)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>8939</v>
+        <v>6142</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>10495</v>
+        <v>7648</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -7951,13 +7951,21 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Common shares, no par value (Note 24)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Long-Term Debt (Note 20)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LongTermDebt</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -7969,10 +7977,10 @@
         </is>
       </c>
       <c r="G70" s="5" t="n">
-        <v>26716</v>
+        <v>37341</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>28995</v>
+        <v>39645</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -7996,17 +8004,17 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Preferred shares (Note 25)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>PreferredStock</t>
-        </is>
-      </c>
+          <t>Junior Subordinated Notes (Note 21)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -8018,10 +8026,10 @@
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>3487</v>
+        <v>8939</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>2499</v>
+        <v>10495</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -8048,27 +8056,25 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Additional paid-in capital</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
+          <t>Common shares, no par value (Note 24)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F72" s="5" t="n">
-        <v>2</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>729</v>
+        <v>26716</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>722</v>
+        <v>28995</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -8095,12 +8101,12 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Retained earnings</t>
+          <t>Preferred shares (Note 25)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>PreferredStock</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8108,14 +8114,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F73" s="5" t="n">
-        <v>5367</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>3773</v>
+        <v>3487</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>819</v>
+        <v>2499</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -8142,12 +8150,12 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Accumulated other comprehensive income/(loss) (Note 26)</t>
+          <t>Additional paid-in capital</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>GainsLossesNotAffectingRetainedEarnings</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8155,16 +8163,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-1434</v>
+        <v>729</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>955</v>
+        <v>722</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -8191,23 +8197,27 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Controlling Interests</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>31398</v>
+        <v>5367</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>33271</v>
+        <v>3773</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>33990</v>
+        <v>819</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -8234,12 +8244,12 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Non-controlling interests (Note 23)</t>
+          <t>Accumulated other comprehensive income/(loss) (Note 26)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>MinorityInterest</t>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8253,10 +8263,10 @@
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>125</v>
+        <v>-1434</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>126</v>
+        <v>955</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -8280,34 +8290,26 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>equity</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>equity total</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
+          <t>Controlling Interests</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>33080</v>
+        <v>31398</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>33396</v>
+        <v>33271</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>34116</v>
+        <v>33990</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -8331,32 +8333,32 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Qualitative goodwill impairment indicators</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>December</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Non-controlling interests (Note 23)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>MinorityInterest</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F78" s="5" t="n">
-        <v>2021</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>125</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>126</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -8382,30 +8384,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Calgary, Canada</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>equity total</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>2022</v>
+        <v>33080</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>33396</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>34116</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -8431,12 +8435,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Qualitative goodwill impairment indicators</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Loans receivable from affiliates (Note 11)</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -8445,13 +8449,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F80" s="5" t="n">
+        <v>2021</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1217</v>
+        <v>31</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -8482,29 +8484,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Calgary, Canada</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Other current assets (Note 7)</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>OtherCurrentAssets</t>
-        </is>
-      </c>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>880</v>
+        <v>2022</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1717</v>
+        <v>14</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -8540,24 +8538,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Plant, Property and Equipment (Note 8)</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NetPPE</t>
-        </is>
-      </c>
+          <t>Loans receivable from affiliates (Note 11)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F82" s="5" t="n">
-        <v>69775</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>70182</v>
+        <v>1217</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -8593,12 +8589,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Equity Investments (Note 10)</t>
+          <t>Other current assets (Note 7)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EquityInvestments</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8607,10 +8603,10 @@
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>6677</v>
+        <v>880</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>8441</v>
+        <v>1717</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -8646,20 +8642,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Long-Term Loans Receivable from Affiliates (Note 11)</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>Plant, Property and Equipment (Note 8)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>1338</v>
+        <v>69775</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>238</v>
+        <v>70182</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Regulatory Assets (Note 12)</t>
+          <t>Equity Investments (Note 10)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>RegulatoryAssets</t>
+          <t>EquityInvestments</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8709,10 +8709,10 @@
         </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>1753</v>
+        <v>6677</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1767</v>
+        <v>8441</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -8748,24 +8748,20 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Goodwill (Note 13)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
+          <t>Long-Term Loans Receivable from Affiliates (Note 11)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F86" s="5" t="n">
-        <v>12679</v>
+        <v>1338</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>12582</v>
+        <v>238</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -8801,12 +8797,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Other Long-Term Assets (Note 14)</t>
+          <t>Regulatory Assets (Note 12)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>OtherNonCurrentAssets</t>
+          <t>RegulatoryAssets</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8815,10 +8811,10 @@
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>979</v>
+        <v>1753</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1403</v>
+        <v>1767</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -8849,25 +8845,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Notes payable (Note 15)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Goodwill (Note 13)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>4176</v>
+        <v>12679</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>5166</v>
+        <v>12582</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -8898,25 +8898,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Accounts payable and other (Note 16)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Other Long-Term Assets (Note 14)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>OtherNonCurrentAssets</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>3816</v>
+        <v>979</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>5099</v>
+        <v>1403</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -8952,26 +8956,20 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Redeemable non-controlling interest (Note 6)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>MinorityInterest</t>
-        </is>
-      </c>
+          <t>Notes payable (Note 15)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>633</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4176</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>5166</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -9007,24 +9005,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Current portion of long-term debt (Note 19)</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>CurrentDebt</t>
-        </is>
-      </c>
+          <t>Accounts payable and other (Note 16)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>1972</v>
+        <v>3816</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>1320</v>
+        <v>5099</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -9060,12 +9054,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Regulatory Liabilities (Note 12)</t>
+          <t>Redeemable non-controlling interest (Note 6)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>RegulatoryLiabilities</t>
+          <t>MinorityInterest</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9074,10 +9068,12 @@
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>4148</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>4300</v>
+        <v>633</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -9113,20 +9109,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Other Long-Term Liabilities (Note 17)</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Current portion of long-term debt (Note 19)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>1475</v>
+        <v>1972</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1059</v>
+        <v>1320</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -9162,20 +9162,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Deferred Income Tax Liabilities (Note 18)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Regulatory Liabilities (Note 12)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>RegulatoryLiabilities</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>5806</v>
+        <v>4148</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>6142</v>
+        <v>4300</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -9211,24 +9215,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Long-Term Debt (Note 19)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>LongTermDebt</t>
-        </is>
-      </c>
+          <t>Other Long-Term Liabilities (Note 17)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>34913</v>
+        <v>1475</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>37341</v>
+        <v>1059</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Junior Subordinated Notes (Note 20)</t>
+          <t>Deferred Income Tax Liabilities (Note 18)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -9274,10 +9274,10 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>8498</v>
+        <v>5806</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>8939</v>
+        <v>6142</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -9313,12 +9313,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Redeemable Non-Controlling Interest (Note 6)</t>
+          <t>Long-Term Debt (Note 19)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>MinorityInterest</t>
+          <t>LongTermDebt</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9327,12 +9327,10 @@
         </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>393</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>34913</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>37341</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -9361,10 +9359,14 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Common shares, no par value (Note 22)</t>
+          <t>Junior Subordinated Notes (Note 20)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -9374,10 +9376,10 @@
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>24488</v>
+        <v>8498</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>26716</v>
+        <v>8939</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -9406,15 +9408,19 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Preferred shares (Note 23)</t>
+          <t>Redeemable Non-Controlling Interest (Note 6)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PreferredStock</t>
+          <t>MinorityInterest</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9423,10 +9429,12 @@
         </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>3980</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>3487</v>
+        <v>393</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -9458,24 +9466,20 @@
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Accumulated other comprehensive loss (Note 24)</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>GainsLossesNotAffectingRetainedEarnings</t>
-        </is>
-      </c>
+          <t>Common shares, no par value (Note 22)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F100" s="5" t="n">
-        <v>-2439</v>
+        <v>24488</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-1434</v>
+        <v>26716</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -9507,12 +9511,12 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Non-controlling interests (Note 21)</t>
+          <t>Preferred shares (Note 23)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>MinorityInterest</t>
+          <t>PreferredStock</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9521,10 +9525,10 @@
         </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>1682</v>
+        <v>3980</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>125</v>
+        <v>3487</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -9550,22 +9554,18 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Operating Activities</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t>Accumulated other comprehensive loss (Note 24)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9573,50 +9573,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="5" t="n">
+        <v>-2439</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-1434</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I102" s="5" t="n">
-        <v>0.000442</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>0.000316</v>
-      </c>
-      <c r="K102" s="5" t="n">
-        <v>0.000433</v>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Operating Activities</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 9</t>
+          <t>Non-controlling interests (Note 21)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>MinorityInterest</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9624,29 +9622,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F103" s="5" t="n">
+        <v>1682</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>125</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="5" t="n">
-        <v>0.000244</v>
-      </c>
-      <c r="J103" s="5" t="n">
-        <v>0.000246</v>
-      </c>
-      <c r="K103" s="5" t="n">
-        <v>0.000247</v>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -9662,10 +9662,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Deferred income tax expense 15</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -9686,16 +9690,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="5" t="n">
+        <v>0.000442</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>5.9e-05</v>
+        <v>0.000316</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>8.000000000000001e-05</v>
+        <v>0.000433</v>
       </c>
     </row>
     <row r="105">
@@ -9711,10 +9713,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Write-downs</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>Depreciation and amortization 9</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -9735,18 +9741,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I105" s="5" t="n">
+        <v>0.000244</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>7e-06</v>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000246</v>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>0.000247</v>
       </c>
     </row>
     <row r="106">
@@ -9762,10 +9764,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Income from equity investments 11</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>Deferred income tax expense 15</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -9786,14 +9792,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="5" t="n">
-        <v>-5e-05</v>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J106" s="5" t="n">
-        <v>-4.9e-05</v>
+        <v>5.9e-05</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>-5.2e-05</v>
+        <v>8.000000000000001e-05</v>
       </c>
     </row>
     <row r="107">
@@ -9804,12 +9812,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Distributions received from operating activities of equity</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Distributions received from operating activities of equity investments 11</t>
+          <t>Write-downs</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -9833,14 +9841,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="5" t="n">
-        <v>7.1e-05</v>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J107" s="5" t="n">
-        <v>6.999999999999999e-05</v>
-      </c>
-      <c r="K107" s="5" t="n">
-        <v>7.4e-05</v>
+        <v>7e-06</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -9851,12 +9863,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Distributions received from operating activities of equity</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Unrealized (gains) losses on financial instruments 21</t>
+          <t>Income from equity investments 11</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -9880,16 +9892,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" s="5" t="n">
+        <v>-5e-05</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>6e-06</v>
+        <v>-4.9e-05</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>-3.6e-05</v>
+        <v>-5.2e-05</v>
       </c>
     </row>
     <row r="109">
@@ -9905,7 +9915,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Non-cash foreign exchange</t>
+          <t>Distributions received from operating activities of equity investments 11</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -9929,16 +9939,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I109" s="5" t="n">
+        <v>7.1e-05</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>-6.9e-05</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>-1e-06</v>
+        <v>7.4e-05</v>
       </c>
     </row>
     <row r="110">
@@ -9954,7 +9962,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Unrealized (gains) losses on financial instruments 21</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -9978,14 +9986,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I110" s="5" t="n">
-        <v>1.3e-05</v>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J110" s="5" t="n">
-        <v>5e-06</v>
+        <v>6e-06</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>7e-06</v>
+        <v>-3.6e-05</v>
       </c>
     </row>
     <row r="111">
@@ -10001,7 +10011,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Increase in operating working capital 22</t>
+          <t>Non-cash foreign exchange</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -10031,10 +10041,10 @@
         </is>
       </c>
       <c r="J111" s="5" t="n">
-        <v>-6.2e-05</v>
+        <v>-6.9e-05</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>-3.5e-05</v>
+        <v>-1e-06</v>
       </c>
     </row>
     <row r="112">
@@ -10050,14 +10060,10 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Net Cash Provided by Operating Activities</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -10078,16 +10084,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I112" s="5" t="n">
+        <v>1.3e-05</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>0.000529</v>
+        <v>5e-06</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>0.000717</v>
+        <v>7e-06</v>
       </c>
     </row>
     <row r="113">
@@ -10098,19 +10102,15 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Distributions received from operating activities of equity</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Capital expenditures</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>CapitalExpenditure</t>
-        </is>
-      </c>
+          <t>Increase in operating working capital 22</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -10131,14 +10131,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" s="5" t="n">
-        <v>-3.7e-05</v>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J113" s="5" t="n">
-        <v>-0.000122</v>
+        <v>-6.2e-05</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>-0.000178</v>
+        <v>-3.5e-05</v>
       </c>
     </row>
     <row r="114">
@@ -10149,15 +10151,19 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Distributions received from operating activities of equity</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Keystone XL contractual recoveries</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>Net Cash Provided by Operating Activities</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -10178,14 +10184,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="5" t="n">
-        <v>8e-06</v>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J114" s="5" t="n">
-        <v>5e-06</v>
+        <v>0.000529</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>3e-06</v>
+        <v>0.000717</v>
       </c>
     </row>
     <row r="115">
@@ -10201,18 +10209,28 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Proceeds from sales of assets, net of transaction costs</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" s="5" t="n">
-        <v>2398</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>3407</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>35</v>
+          <t>Capital expenditures</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -10220,15 +10238,13 @@
         </is>
       </c>
       <c r="I115" s="5" t="n">
-        <v>9.3e-05</v>
+        <v>-3.7e-05</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>3.8e-05</v>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.000122</v>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>-0.000178</v>
       </c>
     </row>
     <row r="116">
@@ -10244,32 +10260,38 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Deferred amounts and other</t>
+          <t>Keystone XL contractual recoveries</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" s="5" t="n">
-        <v>-299</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>-559</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>-447</v>
-      </c>
-      <c r="H116" s="5" t="n">
-        <v>-41</v>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I116" s="5" t="n">
-        <v>-2e-06</v>
+        <v>8e-06</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5e-06</v>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>3e-06</v>
       </c>
     </row>
     <row r="117">
@@ -10285,44 +10307,34 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Net Cash Used in Investing Activities</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from sales of assets, net of transaction costs</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" s="5" t="n">
+        <v>2398</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>3407</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>35</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="5" t="n">
+        <v>9.3e-05</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>-8.000000000000001e-05</v>
-      </c>
-      <c r="K117" s="5" t="n">
-        <v>-0.000175</v>
+        <v>3.8e-05</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -10333,42 +10345,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Senior unsecured debt issued, net of issue costs 17</t>
+          <t>Deferred amounts and other</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E118" s="5" t="n">
+        <v>-299</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>-559</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>-447</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>-2e-06</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>0.003448</v>
+        <v>-1e-06</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -10384,15 +10386,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Junior subordinated debt issued, net of issue costs 17</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>Net Cash Used in Investing Activities</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -10419,12 +10425,10 @@
         </is>
       </c>
       <c r="J119" s="5" t="n">
-        <v>0.001087</v>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.000000000000001e-05</v>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>-0.000175</v>
       </c>
     </row>
     <row r="120">
@@ -10440,7 +10444,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Long-term debt repaid to affiliates of Former Parent 17</t>
+          <t>Senior unsecured debt issued, net of issue costs 17</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -10470,7 +10474,7 @@
         </is>
       </c>
       <c r="J120" s="5" t="n">
-        <v>-0.004722</v>
+        <v>0.003448</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -10491,7 +10495,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Exercised stock options 18</t>
+          <t>Junior subordinated debt issued, net of issue costs 17</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -10521,10 +10525,12 @@
         </is>
       </c>
       <c r="J121" s="5" t="n">
-        <v>9e-06</v>
-      </c>
-      <c r="K121" s="5" t="n">
-        <v>5e-06</v>
+        <v>0.001087</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -10540,14 +10546,10 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Dividends paid</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>CashDividendsPaid</t>
-        </is>
-      </c>
+          <t>Long-term debt repaid to affiliates of Former Parent 17</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -10573,13 +10575,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" s="5" t="n">
-        <v>-0.000416</v>
+      <c r="J122" s="5" t="n">
+        <v>-0.004722</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -10595,7 +10597,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Former Parent's net investment distributions, net</t>
+          <t>Exercised stock options 18</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -10625,12 +10627,10 @@
         </is>
       </c>
       <c r="J123" s="5" t="n">
-        <v>-0.000121</v>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9e-06</v>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>5e-06</v>
       </c>
     </row>
     <row r="124">
@@ -10646,10 +10646,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -10670,16 +10674,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="5" t="n">
-        <v>-3.7e-05</v>
-      </c>
-      <c r="J124" s="5" t="n">
-        <v>-8e-06</v>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>-0.000416</v>
       </c>
     </row>
     <row r="125">
@@ -10695,14 +10701,10 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Net Cash Used in Financing Activities</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Former Parent's net investment distributions, net</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -10729,10 +10731,12 @@
         </is>
       </c>
       <c r="J125" s="5" t="n">
-        <v>-0.000307</v>
-      </c>
-      <c r="K125" s="5" t="n">
-        <v>-0.000411</v>
+        <v>-0.000121</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -10748,7 +10752,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Effect of foreign exchange rate changes on cash and cash equivalents</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -10773,13 +10777,15 @@
         </is>
       </c>
       <c r="I126" s="5" t="n">
-        <v>-6e-06</v>
+        <v>-3.7e-05</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>-7e-06</v>
-      </c>
-      <c r="K126" s="5" t="n">
-        <v>2.1e-05</v>
+        <v>-8e-06</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -10795,12 +10801,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Increase in Cash and Cash Equivalents</t>
+          <t>Net Cash Used in Financing Activities</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -10829,10 +10835,10 @@
         </is>
       </c>
       <c r="J127" s="5" t="n">
-        <v>0.000135</v>
+        <v>-0.000307</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>0.000152</v>
+        <v>-0.000411</v>
       </c>
     </row>
     <row r="128">
@@ -10848,14 +10854,10 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, Beginning of Year</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Effect of foreign exchange rate changes on cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -10877,13 +10879,13 @@
         </is>
       </c>
       <c r="I128" s="5" t="n">
-        <v>4e-06</v>
+        <v>-6e-06</v>
       </c>
       <c r="J128" s="5" t="n">
-        <v>0.000262</v>
+        <v>-7e-06</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>0.000397</v>
+        <v>2.1e-05</v>
       </c>
     </row>
     <row r="129">
@@ -10899,12 +10901,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, End of Year</t>
+          <t>Increase in Cash and Cash Equivalents</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -10927,14 +10929,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="5" t="n">
-        <v>0.000262</v>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J129" s="5" t="n">
-        <v>0.000397</v>
+        <v>0.000135</v>
       </c>
       <c r="K129" s="5" t="n">
-        <v>0.000549</v>
+        <v>0.000152</v>
       </c>
     </row>
     <row r="130">
@@ -10945,17 +10949,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Supplementary Cash Flow Information</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cash income taxes paid</t>
+          <t>Cash and Cash Equivalents, Beginning of Year</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>IncomeTaxPaidSupplementalData</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -10978,16 +10982,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I130" s="5" t="n">
+        <v>4e-06</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>4.9e-05</v>
+        <v>0.000262</v>
       </c>
       <c r="K130" s="5" t="n">
-        <v>3.8e-05</v>
+        <v>0.000397</v>
       </c>
     </row>
     <row r="131">
@@ -10998,17 +11000,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Supplementary Cash Flow Information</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cash interest paid</t>
+          <t>Cash and Cash Equivalents, End of Year</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>InterestPaidSupplementalData</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11031,18 +11033,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I131" s="5" t="n">
+        <v>0.000262</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>0.000397</v>
       </c>
       <c r="K131" s="5" t="n">
-        <v>0.000342</v>
+        <v>0.000549</v>
       </c>
     </row>
     <row r="132">
@@ -11058,10 +11056,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Capital expenditures non-cash accruals</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>Cash income taxes paid</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -11088,10 +11090,10 @@
         </is>
       </c>
       <c r="J132" s="5" t="n">
-        <v>1.9e-05</v>
+        <v>4.9e-05</v>
       </c>
       <c r="K132" s="5" t="n">
-        <v>2.9e-05</v>
+        <v>3.8e-05</v>
       </c>
     </row>
     <row r="133">
@@ -11102,15 +11104,19 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Supplementary Cash Flow Information</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Write downs</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>Cash interest paid</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -11136,13 +11142,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J133" s="5" t="n">
-        <v>7e-06</v>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>0.000342</v>
       </c>
     </row>
     <row r="134">
@@ -11153,19 +11159,15 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Supplementary Cash Flow Information</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Deferred income taxes 16</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>DeferredIncomeTax</t>
-        </is>
-      </c>
+          <t>Capital expenditures non-cash accruals</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -11186,16 +11188,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I134" s="5" t="n">
-        <v>6.7e-05</v>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J134" s="5" t="n">
-        <v>5.9e-05</v>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.9e-05</v>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>2.9e-05</v>
       </c>
     </row>
     <row r="135">
@@ -11206,12 +11208,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Distributions received from operating activities of equity</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Unrealized losses on financial instruments 22</t>
+          <t>Write downs</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -11235,11 +11237,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="5" t="n">
-        <v>2.6e-05</v>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J135" s="5" t="n">
-        <v>6e-06</v>
+        <v>7e-06</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -11255,15 +11259,19 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Distributions received from operating activities of equity</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Non-cash foreign exchange on senior long-term debt issued</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
+          <t>Deferred income taxes 16</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DeferredIncomeTax</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -11284,13 +11292,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I136" s="5" t="n">
+        <v>6.7e-05</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>-6.9e-05</v>
+        <v>5.9e-05</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -11311,7 +11317,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Increase in operating working capital 23</t>
+          <t>Unrealized losses on financial instruments 22</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -11336,10 +11342,10 @@
         </is>
       </c>
       <c r="I137" s="5" t="n">
-        <v>-3.4e-05</v>
+        <v>2.6e-05</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>-6.2e-05</v>
+        <v>6e-06</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -11360,7 +11366,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Net cash provided by operations</t>
+          <t>Non-cash foreign exchange on senior long-term debt issued</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -11384,11 +11390,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" s="5" t="n">
-        <v>0.000779</v>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J138" s="5" t="n">
-        <v>0.000529</v>
+        <v>-6.9e-05</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -11404,19 +11412,15 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Distributions received from operating activities of equity</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Net cash (used in) provided by investing activities</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Increase in operating working capital 23</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -11438,10 +11442,10 @@
         </is>
       </c>
       <c r="I139" s="5" t="n">
-        <v>6.2e-05</v>
+        <v>-3.4e-05</v>
       </c>
       <c r="J139" s="5" t="n">
-        <v>-8.000000000000001e-05</v>
+        <v>-6.2e-05</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -11457,12 +11461,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Distributions received from operating activities of equity</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Senior unsecured debt issued, net of issue costs 18</t>
+          <t>Net cash provided by operations</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -11487,10 +11491,10 @@
         </is>
       </c>
       <c r="I140" s="5" t="n">
-        <v>0.000621</v>
+        <v>0.000779</v>
       </c>
       <c r="J140" s="5" t="n">
-        <v>0.003448</v>
+        <v>0.000529</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -11506,15 +11510,19 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Junior subordinated debt issued, net of issue costs 18</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Net cash (used in) provided by investing activities</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -11535,13 +11543,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I141" s="5" t="n">
+        <v>6.2e-05</v>
       </c>
       <c r="J141" s="5" t="n">
-        <v>0.001087</v>
+        <v>-8.000000000000001e-05</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -11562,7 +11568,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Long-term debt repaid to affiliates of Former Parent 18</t>
+          <t>Senior unsecured debt issued, net of issue costs 18</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -11587,10 +11593,10 @@
         </is>
       </c>
       <c r="I142" s="5" t="n">
-        <v>-0.000971</v>
+        <v>0.000621</v>
       </c>
       <c r="J142" s="5" t="n">
-        <v>-0.004722</v>
+        <v>0.003448</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -11611,7 +11617,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Exercised stock options 19</t>
+          <t>Junior subordinated debt issued, net of issue costs 18</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -11641,7 +11647,7 @@
         </is>
       </c>
       <c r="J143" s="5" t="n">
-        <v>9e-06</v>
+        <v>0.001087</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -11662,7 +11668,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Parent's net investment distributions, net</t>
+          <t>Long-term debt repaid to affiliates of Former Parent 18</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -11687,10 +11693,10 @@
         </is>
       </c>
       <c r="I144" s="5" t="n">
-        <v>-0.00019</v>
+        <v>-0.000971</v>
       </c>
       <c r="J144" s="5" t="n">
-        <v>-0.000121</v>
+        <v>-0.004722</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -11711,14 +11717,10 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Net cash used in financing activities</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Exercised stock options 19</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -11739,11 +11741,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="5" t="n">
-        <v>-0.000577</v>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J145" s="5" t="n">
-        <v>-0.000307</v>
+        <v>9e-06</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -11764,14 +11768,10 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Increase in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Parent's net investment distributions, net</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -11793,10 +11793,10 @@
         </is>
       </c>
       <c r="I146" s="5" t="n">
-        <v>0.000258</v>
+        <v>-0.00019</v>
       </c>
       <c r="J146" s="5" t="n">
-        <v>0.000135</v>
+        <v>-0.000121</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -11812,15 +11812,19 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Supplementary cash flow information</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cash paid of income taxes</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>Net cash used in financing activities</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -11842,10 +11846,10 @@
         </is>
       </c>
       <c r="I147" s="5" t="n">
-        <v>3.4e-05</v>
+        <v>-0.000577</v>
       </c>
       <c r="J147" s="5" t="n">
-        <v>4.9e-05</v>
+        <v>-0.000307</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11861,15 +11865,19 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Supplementary cash flow information</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Capital expenditures non-cash accruals</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
+          <t>Increase in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -11891,10 +11899,10 @@
         </is>
       </c>
       <c r="I148" s="5" t="n">
-        <v>1e-05</v>
+        <v>0.000258</v>
       </c>
       <c r="J148" s="5" t="n">
-        <v>1.9e-05</v>
+        <v>0.000135</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11910,40 +11918,40 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Cash Generated from Operations</t>
+          <t>Supplementary cash flow information</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="n">
-        <v>4433</v>
-      </c>
-      <c r="F149" s="5" t="n">
-        <v>4913</v>
-      </c>
-      <c r="G149" s="5" t="n">
-        <v>2046</v>
-      </c>
-      <c r="H149" s="5" t="n">
-        <v>785</v>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash paid of income taxes</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>3.4e-05</v>
+      </c>
+      <c r="J149" s="5" t="n">
+        <v>4.9e-05</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -11959,40 +11967,40 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Cash Generated from Operations</t>
+          <t>Supplementary cash flow information</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E150" s="5" t="n">
-        <v>2464</v>
-      </c>
-      <c r="F150" s="5" t="n">
-        <v>2590</v>
-      </c>
-      <c r="G150" s="5" t="n">
-        <v>2522</v>
-      </c>
-      <c r="H150" s="5" t="n">
-        <v>2584</v>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Capital expenditures non-cash accruals</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="J150" s="5" t="n">
+        <v>1.9e-05</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -12013,25 +12021,25 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Goodwill and asset impairment charges and other (Notes 6 and 14)</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n">
+        <v>4433</v>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>4913</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>2775</v>
+        <v>2046</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>453</v>
+        <v>785</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -12062,27 +12070,25 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Deferred income taxes (Note 19)</t>
+          <t>Depreciation and amortization</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>DeferredIncomeTax</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="n">
+        <v>2464</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>-58</v>
+        <v>2590</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>-185</v>
+        <v>2522</v>
       </c>
       <c r="H152" s="5" t="n">
-        <v>174</v>
+        <v>2584</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -12113,7 +12119,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Income from equity investments (Note 11)</t>
+          <t>Goodwill and asset impairment charges and other (Notes 6 and 14)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -12122,14 +12128,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F153" s="5" t="n">
-        <v>-1019</v>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>-898</v>
+        <v>2775</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>-1054</v>
+        <v>453</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -12160,27 +12168,27 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Impairment of equity investment (Notes 7 and 11)</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
+          <t>Deferred income taxes (Note 19)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>DeferredIncomeTax</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F154" s="5" t="n">
+        <v>-58</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>-185</v>
       </c>
       <c r="H154" s="5" t="n">
-        <v>3048</v>
+        <v>174</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -12211,7 +12219,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Distributions received from operating activities of equity investments (Note 11)</t>
+          <t>Income from equity investments (Note 11)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -12221,13 +12229,13 @@
         </is>
       </c>
       <c r="F155" s="5" t="n">
-        <v>1123</v>
+        <v>-1019</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>975</v>
+        <v>-898</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>1025</v>
+        <v>-1054</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -12258,7 +12266,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Employee post-retirement benefits funding, net of expense (Note 27)</t>
+          <t>Impairment of equity investment (Notes 7 and 11)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -12267,14 +12275,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F156" s="5" t="n">
-        <v>-19</v>
-      </c>
-      <c r="G156" s="5" t="n">
-        <v>-5</v>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H156" s="5" t="n">
-        <v>-29</v>
+        <v>3048</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -12305,7 +12317,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Net (gain)/loss on sale of assets (Note 30)</t>
+          <t>Distributions received from operating activities of equity investments (Note 11)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -12315,15 +12327,13 @@
         </is>
       </c>
       <c r="F157" s="5" t="n">
-        <v>50</v>
+        <v>1123</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>-30</v>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>975</v>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>1025</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -12354,21 +12364,23 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Equity allowance for funds used during construction</t>
+          <t>Employee post-retirement benefits funding, net of expense (Note 27)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" s="5" t="n">
-        <v>-299</v>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F158" s="5" t="n">
-        <v>-235</v>
+        <v>-19</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>-191</v>
+        <v>-5</v>
       </c>
       <c r="H158" s="5" t="n">
-        <v>-248</v>
+        <v>-29</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -12399,21 +12411,25 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Unrealized losses/(gains) on financial instruments</t>
+          <t>Net (gain)/loss on sale of assets (Note 30)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" s="5" t="n">
-        <v>-134</v>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F159" s="5" t="n">
-        <v>-103</v>
+        <v>50</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>194</v>
-      </c>
-      <c r="H159" s="5" t="n">
-        <v>135</v>
+        <v>-30</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -12444,27 +12460,21 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Expected credit loss provision</t>
+          <t>Equity allowance for funds used during construction</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E160" s="5" t="n">
+        <v>-299</v>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>-235</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>-191</v>
       </c>
       <c r="H160" s="5" t="n">
-        <v>163</v>
+        <v>-248</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -12495,23 +12505,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Foreign exchange losses on loan receivable from affiliate (Note 12)</t>
+          <t>Unrealized losses/(gains) on financial instruments</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E161" s="5" t="n">
+        <v>-134</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>86</v>
+        <v>-103</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>41</v>
+        <v>194</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -12542,21 +12550,27 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Expected credit loss provision</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" s="5" t="n">
-        <v>-46</v>
-      </c>
-      <c r="F162" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="G162" s="5" t="n">
-        <v>-67</v>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H162" s="5" t="n">
-        <v>-50</v>
+        <v>163</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -12587,7 +12601,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Increase in operating working capital (Note 29)</t>
+          <t>Foreign exchange losses on loan receivable from affiliate (Note 12)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -12597,13 +12611,13 @@
         </is>
       </c>
       <c r="F163" s="5" t="n">
-        <v>-327</v>
+        <v>86</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>-287</v>
+        <v>41</v>
       </c>
       <c r="H163" s="5" t="n">
-        <v>-639</v>
+        <v>28</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -12634,21 +12648,21 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Net cash provided by operations</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" s="5" t="n">
-        <v>7082</v>
+        <v>-46</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>7058</v>
+        <v>57</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>6890</v>
+        <v>-67</v>
       </c>
       <c r="H164" s="5" t="n">
-        <v>6375</v>
+        <v>-50</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -12674,30 +12688,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Cash Generated from Operations</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Capital expenditures (Note 4)</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>CapitalExpenditure</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="n">
-        <v>-7475</v>
+          <t>Increase in operating working capital (Note 29)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F165" s="5" t="n">
-        <v>-8013</v>
+        <v>-327</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>-5924</v>
+        <v>-287</v>
       </c>
       <c r="H165" s="5" t="n">
-        <v>-6678</v>
+        <v>-639</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -12723,28 +12735,26 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Cash Generated from Operations</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Capital projects in development (Note 4)</t>
+          <t>Net cash provided by operations</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" s="5" t="n">
-        <v>-707</v>
+        <v>7082</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>-122</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7058</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>6890</v>
       </c>
       <c r="H166" s="5" t="n">
-        <v>-49</v>
+        <v>6375</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -12775,23 +12785,25 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Contributions to equity investments (Notes 4, 7 and 11)</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Capital expenditures (Note 4)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="n">
+        <v>-7475</v>
       </c>
       <c r="F167" s="5" t="n">
-        <v>-765</v>
+        <v>-8013</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>-1210</v>
+        <v>-5924</v>
       </c>
       <c r="H167" s="5" t="n">
-        <v>-3433</v>
+        <v>-6678</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -12822,19 +12834,15 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Keystone XL contractual recoveries (Note 6)</t>
+          <t>Capital projects in development (Note 4)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E168" s="5" t="n">
+        <v>-707</v>
+      </c>
+      <c r="F168" s="5" t="n">
+        <v>-122</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -12842,7 +12850,7 @@
         </is>
       </c>
       <c r="H168" s="5" t="n">
-        <v>571</v>
+        <v>-49</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -12873,7 +12881,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Loans to affiliate issued, net (Notes 7 and 12)</t>
+          <t>Contributions to equity investments (Notes 4, 7 and 11)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -12882,16 +12890,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F169" s="5" t="n">
+        <v>-765</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>-239</v>
+        <v>-1210</v>
       </c>
       <c r="H169" s="5" t="n">
-        <v>-11</v>
+        <v>-3433</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -12922,7 +12928,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Other distributions from equity investments (Note 11)</t>
+          <t>Keystone XL contractual recoveries (Note 6)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -12936,11 +12942,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G170" s="5" t="n">
-        <v>73</v>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H170" s="5" t="n">
-        <v>2632</v>
+        <v>571</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -12971,25 +12979,25 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="n">
-        <v>-6872</v>
-      </c>
-      <c r="F171" s="5" t="n">
-        <v>-6052</v>
+          <t>Loans to affiliate issued, net (Notes 7 and 12)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>-7712</v>
+        <v>-239</v>
       </c>
       <c r="H171" s="5" t="n">
-        <v>-7009</v>
+        <v>-11</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -13015,26 +13023,30 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Notes payable issued/(repaid), net</t>
+          <t>Other distributions from equity investments (Note 11)</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" s="5" t="n">
-        <v>1656</v>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>-220</v>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>1003</v>
+        <v>73</v>
       </c>
       <c r="H172" s="5" t="n">
-        <v>766</v>
+        <v>2632</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -13060,26 +13072,30 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Long-term debt issued, net of issue costs</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E173" s="5" t="n">
-        <v>3024</v>
+        <v>-6872</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>5770</v>
+        <v>-6052</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>10730</v>
+        <v>-7712</v>
       </c>
       <c r="H173" s="5" t="n">
-        <v>2508</v>
+        <v>-7009</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -13110,21 +13126,21 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Long-term debt repaid</t>
+          <t>Notes payable issued/(repaid), net</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" s="5" t="n">
-        <v>-3502</v>
+        <v>1656</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>-3977</v>
+        <v>-220</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>-7758</v>
+        <v>1003</v>
       </c>
       <c r="H174" s="5" t="n">
-        <v>-1338</v>
+        <v>766</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -13155,23 +13171,21 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Junior subordinated notes issued, net of issue costs</t>
+          <t>Long-term debt issued, net of issue costs</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" s="5" t="n">
-        <v>1436</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3024</v>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>5770</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>495</v>
+        <v>10730</v>
       </c>
       <c r="H175" s="5" t="n">
-        <v>1008</v>
+        <v>2508</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -13202,23 +13216,21 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Gain/(loss) on settlement of financial instruments</t>
+          <t>Long-term debt repaid</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E176" s="5" t="n">
+        <v>-3502</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>-130</v>
+        <v>-3977</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>-10</v>
+        <v>-7758</v>
       </c>
       <c r="H176" s="5" t="n">
-        <v>23</v>
+        <v>-1338</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -13249,14 +13261,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Redeemable non-controlling interest repurchased (Note 6)</t>
+          <t>Junior subordinated notes issued, net of issue costs</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E177" s="5" t="n">
+        <v>1436</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13264,12 +13274,10 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>-633</v>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>495</v>
+      </c>
+      <c r="H177" s="5" t="n">
+        <v>1008</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -13300,7 +13308,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Contributions from redeemable non-controlling interest (Note 6)</t>
+          <t>Gain/(loss) on settlement of financial instruments</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -13310,17 +13318,13 @@
         </is>
       </c>
       <c r="F178" s="5" t="n">
-        <v>1033</v>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-130</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H178" s="5" t="n">
+        <v>23</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -13351,21 +13355,27 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Dividends on common shares</t>
+          <t>Redeemable non-controlling interest repurchased (Note 6)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" s="5" t="n">
-        <v>-1798</v>
-      </c>
-      <c r="F179" s="5" t="n">
-        <v>-2987</v>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>-3317</v>
-      </c>
-      <c r="H179" s="5" t="n">
-        <v>-3192</v>
+        <v>-633</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -13396,21 +13406,27 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Dividends on preferred shares</t>
+          <t>Contributions from redeemable non-controlling interest (Note 6)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" s="5" t="n">
-        <v>-160</v>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F180" s="5" t="n">
-        <v>-159</v>
-      </c>
-      <c r="G180" s="5" t="n">
-        <v>-141</v>
-      </c>
-      <c r="H180" s="5" t="n">
-        <v>-106</v>
+        <v>1033</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -13441,21 +13457,21 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Distributions to non-controlling interests</t>
+          <t>Dividends on common shares</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" s="5" t="n">
-        <v>-216</v>
+        <v>-1798</v>
       </c>
       <c r="F181" s="5" t="n">
-        <v>-221</v>
+        <v>-2987</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>-74</v>
+        <v>-3317</v>
       </c>
       <c r="H181" s="5" t="n">
-        <v>-44</v>
+        <v>-3192</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -13486,25 +13502,21 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Distributions on Class C Interests (Note 6)</t>
+          <t>Dividends on preferred shares</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E182" s="5" t="n">
+        <v>-160</v>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>-159</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>-16</v>
+        <v>-141</v>
       </c>
       <c r="H182" s="5" t="n">
-        <v>-43</v>
+        <v>-106</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -13535,21 +13547,21 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Common shares issued, net of issue costs</t>
+          <t>Distributions to non-controlling interests</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" s="5" t="n">
-        <v>253</v>
+        <v>-216</v>
       </c>
       <c r="F183" s="5" t="n">
-        <v>91</v>
+        <v>-221</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>148</v>
+        <v>-74</v>
       </c>
       <c r="H183" s="5" t="n">
-        <v>1905</v>
+        <v>-44</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -13580,7 +13592,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Preferred shares redeemed (Note 25)</t>
+          <t>Distributions on Class C Interests (Note 6)</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -13595,10 +13607,10 @@
         </is>
       </c>
       <c r="G184" s="5" t="n">
-        <v>-500</v>
+        <v>-16</v>
       </c>
       <c r="H184" s="5" t="n">
-        <v>-1000</v>
+        <v>-43</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -13629,27 +13641,21 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Acquisition of TC PipeLines, LP transaction costs (Note 23)</t>
+          <t>Common shares issued, net of issue costs</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E185" s="5" t="n">
+        <v>253</v>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>91</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>-15</v>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>148</v>
+      </c>
+      <c r="H185" s="5" t="n">
+        <v>1905</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -13680,27 +13686,25 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Net cash provided by/(used in) financing activities</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Preferred shares redeemed (Note 25)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F186" s="5" t="n">
-        <v>-800</v>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>-88</v>
+        <v>-500</v>
       </c>
       <c r="H186" s="5" t="n">
-        <v>487</v>
+        <v>-1000</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -13731,21 +13735,27 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Effect of Foreign Exchange Rate Changes on Cash and Cash Equivalents</t>
+          <t>Acquisition of TC PipeLines, LP transaction costs (Note 23)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" s="5" t="n">
-        <v>-6</v>
-      </c>
-      <c r="F187" s="5" t="n">
-        <v>-19</v>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>94</v>
+        <v>-15</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -13776,25 +13786,27 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>(Decrease)/Increase in Cash and Cash Equivalents</t>
+          <t>Net cash provided by/(used in) financing activities</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E188" s="5" t="n">
-        <v>897</v>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F188" s="5" t="n">
-        <v>187</v>
+        <v>-800</v>
       </c>
       <c r="G188" s="5" t="n">
-        <v>-857</v>
+        <v>-88</v>
       </c>
       <c r="H188" s="5" t="n">
-        <v>-53</v>
+        <v>487</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -13820,26 +13832,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Beginning of year</t>
+          <t>Effect of Foreign Exchange Rate Changes on Cash and Cash Equivalents</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" s="5" t="n">
-        <v>446</v>
+        <v>-6</v>
       </c>
       <c r="F189" s="5" t="n">
-        <v>1343</v>
+        <v>-19</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>1530</v>
+        <v>53</v>
       </c>
       <c r="H189" s="5" t="n">
-        <v>673</v>
+        <v>94</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -13865,26 +13877,30 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>End of year</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>(Decrease)/Increase in Cash and Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E190" s="5" t="n">
-        <v>1343</v>
+        <v>897</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>1530</v>
+        <v>187</v>
       </c>
       <c r="G190" s="5" t="n">
-        <v>673</v>
+        <v>-857</v>
       </c>
       <c r="H190" s="5" t="n">
-        <v>620</v>
+        <v>-53</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -13910,32 +13926,26 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Cash Generated from Operations</t>
+          <t>Cash and Cash Equivalents</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Asset impairment charge and other (Note 6)</t>
+          <t>Beginning of year</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E191" s="5" t="n">
+        <v>446</v>
+      </c>
+      <c r="F191" s="5" t="n">
+        <v>1343</v>
       </c>
       <c r="G191" s="5" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1530</v>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>673</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -13961,32 +13971,26 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Cash Generated from Operations</t>
+          <t>Cash and Cash Equivalents</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Deferred income taxes (Note 18)</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>DeferredIncomeTax</t>
-        </is>
-      </c>
+          <t>End of year</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
       <c r="E192" s="5" t="n">
-        <v>55</v>
+        <v>1343</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>-58</v>
+        <v>1530</v>
       </c>
       <c r="G192" s="5" t="n">
-        <v>-185</v>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>673</v>
+      </c>
+      <c r="H192" s="5" t="n">
+        <v>620</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -14017,18 +14021,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Income from equity investments (Note 10)</t>
+          <t>Asset impairment charge and other (Note 6)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" s="5" t="n">
-        <v>-920</v>
-      </c>
-      <c r="F193" s="5" t="n">
-        <v>-1019</v>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>-898</v>
+        <v>2775</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -14064,18 +14072,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Distributions received from operating activities of equity investments (Note 10)</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
+          <t>Deferred income taxes (Note 18)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>DeferredIncomeTax</t>
+        </is>
+      </c>
       <c r="E194" s="5" t="n">
-        <v>1213</v>
+        <v>55</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>1123</v>
+        <v>-58</v>
       </c>
       <c r="G194" s="5" t="n">
-        <v>975</v>
+        <v>-185</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -14111,18 +14123,18 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Employee post-retirement benefits funding, net of expense (Note 25)</t>
+          <t>Income from equity investments (Note 10)</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" s="5" t="n">
-        <v>-45</v>
+        <v>-920</v>
       </c>
       <c r="F195" s="5" t="n">
-        <v>-19</v>
+        <v>-1019</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>-5</v>
+        <v>-898</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -14158,18 +14170,18 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Net (gain)/loss on assets sold/held for sale (Note 28)</t>
+          <t>Distributions received from operating activities of equity investments (Note 10)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" s="5" t="n">
-        <v>121</v>
+        <v>1213</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>50</v>
+        <v>1123</v>
       </c>
       <c r="G196" s="5" t="n">
-        <v>-30</v>
+        <v>975</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -14205,18 +14217,18 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Foreign exchange losses/(gains) on loan receivable from affiliate (Note 11)</t>
+          <t>Employee post-retirement benefits funding, net of expense (Note 25)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" s="5" t="n">
-        <v>-53</v>
+        <v>-45</v>
       </c>
       <c r="F197" s="5" t="n">
-        <v>86</v>
+        <v>-19</v>
       </c>
       <c r="G197" s="5" t="n">
-        <v>41</v>
+        <v>-5</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -14252,18 +14264,18 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>(Increase)/decrease in operating working capital (Note 27)</t>
+          <t>Net (gain)/loss on assets sold/held for sale (Note 28)</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" s="5" t="n">
-        <v>293</v>
+        <v>121</v>
       </c>
       <c r="F198" s="5" t="n">
-        <v>-327</v>
+        <v>50</v>
       </c>
       <c r="G198" s="5" t="n">
-        <v>-287</v>
+        <v>-30</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -14294,23 +14306,23 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Cash Generated from Operations</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Contributions to equity investments (Notes 4 and 10)</t>
+          <t>Foreign exchange losses/(gains) on loan receivable from affiliate (Note 11)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" s="5" t="n">
-        <v>-602</v>
+        <v>-53</v>
       </c>
       <c r="F199" s="5" t="n">
-        <v>-765</v>
+        <v>86</v>
       </c>
       <c r="G199" s="5" t="n">
-        <v>-1210</v>
+        <v>41</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -14341,27 +14353,23 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Cash Generated from Operations</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Loan to affiliate (Note 11)</t>
+          <t>(Increase)/decrease in operating working capital (Note 27)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E200" s="5" t="n">
+        <v>293</v>
+      </c>
+      <c r="F200" s="5" t="n">
+        <v>-327</v>
       </c>
       <c r="G200" s="5" t="n">
-        <v>-239</v>
+        <v>-287</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -14397,22 +14405,18 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Contributions to equity investments (Notes 4 and 10)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E201" s="5" t="n">
+        <v>-602</v>
       </c>
       <c r="F201" s="5" t="n">
-        <v>-88</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-765</v>
+      </c>
+      <c r="G201" s="5" t="n">
+        <v>-1210</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -14448,12 +14452,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Other distributions from equity investments (Note 10)</t>
+          <t>Loan to affiliate (Note 11)</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
-      <c r="E202" s="5" t="n">
-        <v>186</v>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -14461,7 +14467,7 @@
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>73</v>
+        <v>-239</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -14497,17 +14503,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Payment for unredeemed shares of Columbia Pipeline Group, Inc. (Note 28)</t>
+          <t>Acquisition</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
-      <c r="E203" s="5" t="n">
-        <v>-373</v>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>-88</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -14543,25 +14549,25 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Loss on settlement of financial instruments (Note 26)</t>
+          <t>Other distributions from equity investments (Note 10)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F204" s="5" t="n">
-        <v>-130</v>
+      <c r="E204" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>-10</v>
+        <v>73</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -14592,27 +14598,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Preferred shares redeemed (Note 23)</t>
+          <t>Payment for unredeemed shares of Columbia Pipeline Group, Inc. (Note 28)</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E205" s="5" t="n">
+        <v>-373</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G205" s="5" t="n">
-        <v>-500</v>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -14648,7 +14654,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Acquisition of TC PipeLines, LP transaction costs (Note 21)</t>
+          <t>Loss on settlement of financial instruments (Note 26)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -14657,13 +14663,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F206" s="5" t="n">
+        <v>-130</v>
       </c>
       <c r="G206" s="5" t="n">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -14699,22 +14703,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Net cash (used in)/provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E207" s="5" t="n">
-        <v>693</v>
-      </c>
-      <c r="F207" s="5" t="n">
-        <v>-800</v>
+          <t>Preferred shares redeemed (Note 23)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>-88</v>
+        <v>-500</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -14740,20 +14744,20 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Financing Activities</t>
+        </is>
+      </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Revenues 6</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Acquisition of TC PipeLines, LP transaction costs (Note 21)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -14764,53 +14768,59 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G208" s="5" t="n">
+        <v>-15</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I208" s="5" t="n">
-        <v>0.002005</v>
-      </c>
-      <c r="J208" s="5" t="n">
-        <v>0.00212</v>
-      </c>
-      <c r="K208" s="5" t="n">
-        <v>0.001986</v>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Financing Activities</t>
+        </is>
+      </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Income from Equity Investments 11</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash (used in)/provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="n">
+        <v>693</v>
+      </c>
+      <c r="F209" s="5" t="n">
+        <v>-800</v>
+      </c>
+      <c r="G209" s="5" t="n">
+        <v>-88</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -14822,11 +14832,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J209" s="5" t="n">
-        <v>4.9e-05</v>
-      </c>
-      <c r="K209" s="5" t="n">
-        <v>5.2e-05</v>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -14835,37 +14849,45 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Operating and Other Expenses</t>
-        </is>
-      </c>
+      <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Plant operating costs and other</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" s="5" t="n">
-        <v>3913</v>
-      </c>
-      <c r="F210" s="5" t="n">
-        <v>3878</v>
-      </c>
-      <c r="G210" s="5" t="n">
-        <v>4098</v>
-      </c>
-      <c r="H210" s="5" t="n">
-        <v>4932</v>
+          <t>Revenues 6</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I210" s="5" t="n">
-        <v>0.00071</v>
+        <v>0.002005</v>
       </c>
       <c r="J210" s="5" t="n">
-        <v>0.000738</v>
+        <v>0.00212</v>
       </c>
       <c r="K210" s="5" t="n">
-        <v>0.000719</v>
+        <v>0.001986</v>
       </c>
     </row>
     <row r="211">
@@ -14874,39 +14896,43 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Operating and Other Expenses</t>
-        </is>
-      </c>
+      <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Commodity purchases resold</t>
+          <t>Income from Equity Investments 11</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
-      <c r="E211" s="5" t="n">
-        <v>365</v>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G211" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="H211" s="5" t="n">
-        <v>534</v>
-      </c>
-      <c r="I211" s="5" t="n">
-        <v>0.000351</v>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J211" s="5" t="n">
-        <v>0.000376</v>
+        <v>4.9e-05</v>
       </c>
       <c r="K211" s="5" t="n">
-        <v>0.000313</v>
+        <v>5.2e-05</v>
       </c>
     </row>
     <row r="212">
@@ -14922,42 +14948,30 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 9</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Plant operating costs and other</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" s="5" t="n">
+        <v>3913</v>
+      </c>
+      <c r="F212" s="5" t="n">
+        <v>3878</v>
+      </c>
+      <c r="G212" s="5" t="n">
+        <v>4098</v>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>4932</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>0.000244</v>
+        <v>0.00071</v>
       </c>
       <c r="J212" s="5" t="n">
-        <v>0.000246</v>
+        <v>0.000738</v>
       </c>
       <c r="K212" s="5" t="n">
-        <v>0.000247</v>
+        <v>0.000719</v>
       </c>
     </row>
     <row r="213">
@@ -14973,40 +14987,32 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Commodity purchases resold</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E213" s="5" t="n">
+        <v>365</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G213" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="H213" s="5" t="n">
+        <v>534</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>0.000351</v>
       </c>
       <c r="J213" s="5" t="n">
-        <v>1.5e-05</v>
+        <v>0.000376</v>
       </c>
       <c r="K213" s="5" t="n">
-        <v>-8e-06</v>
+        <v>0.000313</v>
       </c>
     </row>
     <row r="214">
@@ -15022,34 +15028,42 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Operating and Other Expenses total</t>
+          <t>Depreciation and amortization 9</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="n">
-        <v>7469</v>
-      </c>
-      <c r="F214" s="5" t="n">
-        <v>7195</v>
-      </c>
-      <c r="G214" s="5" t="n">
-        <v>10256</v>
-      </c>
-      <c r="H214" s="5" t="n">
-        <v>9351</v>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I214" s="5" t="n">
-        <v>0.001305</v>
+        <v>0.000244</v>
       </c>
       <c r="J214" s="5" t="n">
-        <v>0.001375</v>
+        <v>0.000246</v>
       </c>
       <c r="K214" s="5" t="n">
-        <v>0.001271</v>
+        <v>0.000247</v>
       </c>
     </row>
     <row r="215">
@@ -15065,14 +15079,10 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Other Income 23</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -15098,13 +15108,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J215" s="5" t="n">
+        <v>1.5e-05</v>
       </c>
       <c r="K215" s="5" t="n">
-        <v>-2e-05</v>
+        <v>-8e-06</v>
       </c>
     </row>
     <row r="216">
@@ -15115,49 +15123,39 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Financial Charges</t>
+          <t>Operating and Other Expenses</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Interest expense 17</t>
+          <t>Operating and Other Expenses total</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="n">
+        <v>7469</v>
+      </c>
+      <c r="F216" s="5" t="n">
+        <v>7195</v>
+      </c>
+      <c r="G216" s="5" t="n">
+        <v>10256</v>
+      </c>
+      <c r="H216" s="5" t="n">
+        <v>9351</v>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>0.001305</v>
       </c>
       <c r="J216" s="5" t="n">
-        <v>0.000388</v>
+        <v>0.001375</v>
       </c>
       <c r="K216" s="5" t="n">
-        <v>0.000331</v>
+        <v>0.001271</v>
       </c>
     </row>
     <row r="217">
@@ -15168,15 +15166,19 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Financial Charges</t>
+          <t>Operating and Other Expenses</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Interest income and other 17</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
+          <t>Other Income 23</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -15202,11 +15204,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J217" s="5" t="n">
-        <v>-1.2e-05</v>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K217" s="5" t="n">
-        <v>-4.1e-05</v>
+        <v>-2e-05</v>
       </c>
     </row>
     <row r="218">
@@ -15222,21 +15226,33 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Financial Charges total</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" s="5" t="n">
-        <v>1398</v>
-      </c>
-      <c r="F218" s="5" t="n">
-        <v>1666</v>
-      </c>
-      <c r="G218" s="5" t="n">
-        <v>1893</v>
-      </c>
-      <c r="H218" s="5" t="n">
-        <v>2258</v>
+          <t>Interest expense 17</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -15244,10 +15260,10 @@
         </is>
       </c>
       <c r="J218" s="5" t="n">
-        <v>0.000376</v>
+        <v>0.000388</v>
       </c>
       <c r="K218" s="5" t="n">
-        <v>0.00027</v>
+        <v>0.000331</v>
       </c>
     </row>
     <row r="219">
@@ -15263,25 +15279,29 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Income before Income Taxes</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E219" s="5" t="n">
-        <v>5187</v>
-      </c>
-      <c r="F219" s="5" t="n">
-        <v>5107</v>
-      </c>
-      <c r="G219" s="5" t="n">
-        <v>2166</v>
-      </c>
-      <c r="H219" s="5" t="n">
-        <v>1374</v>
+          <t>Interest income and other 17</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -15289,10 +15309,10 @@
         </is>
       </c>
       <c r="J219" s="5" t="n">
-        <v>0.000418</v>
+        <v>-1.2e-05</v>
       </c>
       <c r="K219" s="5" t="n">
-        <v>0.000497</v>
+        <v>-4.1e-05</v>
       </c>
     </row>
     <row r="220">
@@ -15303,34 +15323,26 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Financial Charges</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Current 15</t>
+          <t>Financial Charges total</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E220" s="5" t="n">
+        <v>1398</v>
+      </c>
+      <c r="F220" s="5" t="n">
+        <v>1666</v>
+      </c>
+      <c r="G220" s="5" t="n">
+        <v>1893</v>
+      </c>
+      <c r="H220" s="5" t="n">
+        <v>2258</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -15338,10 +15350,10 @@
         </is>
       </c>
       <c r="J220" s="5" t="n">
-        <v>4.3e-05</v>
+        <v>0.000376</v>
       </c>
       <c r="K220" s="5" t="n">
-        <v>-1.6e-05</v>
+        <v>0.00027</v>
       </c>
     </row>
     <row r="221">
@@ -15352,34 +15364,30 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Financial Charges</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Deferred 15</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Income before Income Taxes</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="n">
+        <v>5187</v>
+      </c>
+      <c r="F221" s="5" t="n">
+        <v>5107</v>
+      </c>
+      <c r="G221" s="5" t="n">
+        <v>2166</v>
+      </c>
+      <c r="H221" s="5" t="n">
+        <v>1374</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -15387,10 +15395,10 @@
         </is>
       </c>
       <c r="J221" s="5" t="n">
-        <v>5.9e-05</v>
+        <v>0.000418</v>
       </c>
       <c r="K221" s="5" t="n">
-        <v>8.000000000000001e-05</v>
+        <v>0.000497</v>
       </c>
     </row>
     <row r="222">
@@ -15406,14 +15414,10 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery) total</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Current 15</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -15440,10 +15444,10 @@
         </is>
       </c>
       <c r="J222" s="5" t="n">
-        <v>0.000102</v>
+        <v>4.3e-05</v>
       </c>
       <c r="K222" s="5" t="n">
-        <v>6.4e-05</v>
+        <v>-1.6e-05</v>
       </c>
     </row>
     <row r="223">
@@ -15459,14 +15463,10 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Deferred 15</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -15493,10 +15493,10 @@
         </is>
       </c>
       <c r="J223" s="5" t="n">
-        <v>0.000316</v>
+        <v>5.9e-05</v>
       </c>
       <c r="K223" s="5" t="n">
-        <v>0.000433</v>
+        <v>8.000000000000001e-05</v>
       </c>
     </row>
     <row r="224">
@@ -15512,10 +15512,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Net Income per Common Share - Basic 19</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
+          <t>Income tax expense (recovery) total</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -15542,10 +15546,10 @@
         </is>
       </c>
       <c r="J224" s="5" t="n">
-        <v>1.52e-06</v>
+        <v>0.000102</v>
       </c>
       <c r="K224" s="5" t="n">
-        <v>2.08e-06</v>
+        <v>6.4e-05</v>
       </c>
     </row>
     <row r="225">
@@ -15561,10 +15565,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Net Income per Common Share - Diluted 19</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -15591,10 +15599,10 @@
         </is>
       </c>
       <c r="J225" s="5" t="n">
-        <v>1.52e-06</v>
+        <v>0.000316</v>
       </c>
       <c r="K225" s="5" t="n">
-        <v>2.07e-06</v>
+        <v>0.000433</v>
       </c>
     </row>
     <row r="226">
@@ -15610,7 +15618,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Common Shares (millions) - Basic 19</t>
+          <t>Net Income per Common Share - Basic 19</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -15640,10 +15648,10 @@
         </is>
       </c>
       <c r="J226" s="5" t="n">
-        <v>0.0002076</v>
+        <v>1.52e-06</v>
       </c>
       <c r="K226" s="5" t="n">
-        <v>0.0002082</v>
+        <v>2.08e-06</v>
       </c>
     </row>
     <row r="227">
@@ -15659,7 +15667,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Common Shares (millions) - Diluted 19</t>
+          <t>Net Income per Common Share - Diluted 19</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -15689,10 +15697,10 @@
         </is>
       </c>
       <c r="J227" s="5" t="n">
-        <v>0.0002082</v>
+        <v>1.52e-06</v>
       </c>
       <c r="K227" s="5" t="n">
-        <v>0.0002088</v>
+        <v>2.07e-06</v>
       </c>
     </row>
     <row r="228">
@@ -15708,14 +15716,10 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Weighted Average Number of Common Shares (millions) - Basic 19</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -15742,10 +15746,10 @@
         </is>
       </c>
       <c r="J228" s="5" t="n">
-        <v>0.000316</v>
+        <v>0.0002076</v>
       </c>
       <c r="K228" s="5" t="n">
-        <v>0.000433</v>
+        <v>0.0002082</v>
       </c>
     </row>
     <row r="229">
@@ -15761,7 +15765,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Foreign currency translation - net investment hedge</t>
+          <t>Weighted Average Number of Common Shares (millions) - Diluted 19</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -15791,10 +15795,10 @@
         </is>
       </c>
       <c r="J229" s="5" t="n">
-        <v>-6.7e-05</v>
+        <v>0.0002082</v>
       </c>
       <c r="K229" s="5" t="n">
-        <v>5.5e-05</v>
+        <v>0.0002088</v>
       </c>
     </row>
     <row r="230">
@@ -15810,10 +15814,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Foreign currency translation - other</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -15840,10 +15848,10 @@
         </is>
       </c>
       <c r="J230" s="5" t="n">
-        <v>-9e-06</v>
+        <v>0.000316</v>
       </c>
       <c r="K230" s="5" t="n">
-        <v>1.7e-05</v>
+        <v>0.000433</v>
       </c>
     </row>
     <row r="231">
@@ -15859,7 +15867,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Separation-related pension adjustment</t>
+          <t>Foreign currency translation - net investment hedge</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -15889,12 +15897,10 @@
         </is>
       </c>
       <c r="J231" s="5" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.7e-05</v>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>5.5e-05</v>
       </c>
     </row>
     <row r="232">
@@ -15910,7 +15916,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Changes in pension estimate 20</t>
+          <t>Foreign currency translation - other</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -15940,10 +15946,10 @@
         </is>
       </c>
       <c r="J232" s="5" t="n">
-        <v>3e-06</v>
+        <v>-9e-06</v>
       </c>
       <c r="K232" s="5" t="n">
-        <v>5e-06</v>
+        <v>1.7e-05</v>
       </c>
     </row>
     <row r="233">
@@ -15959,7 +15965,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Comprehensive Income</t>
+          <t>Separation-related pension adjustment</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -15989,10 +15995,12 @@
         </is>
       </c>
       <c r="J233" s="5" t="n">
-        <v>0.000246</v>
-      </c>
-      <c r="K233" s="5" t="n">
-        <v>0.00051</v>
+        <v>3e-06</v>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -16001,10 +16009,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Income from equity investments 11</t>
+          <t>Changes in pension estimate 20</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -16028,16 +16040,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I234" s="5" t="n">
-        <v>5e-05</v>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J234" s="5" t="n">
-        <v>4.9e-05</v>
-      </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-06</v>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>5e-06</v>
       </c>
     </row>
     <row r="235">
@@ -16048,19 +16060,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Operating and Other Expenses</t>
+          <t>Income tax expense (recovery)</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Interest expense 18</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Comprehensive Income</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -16081,16 +16089,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I235" s="5" t="n">
-        <v>0.00022</v>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J235" s="5" t="n">
-        <v>0.000388</v>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000246</v>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>0.00051</v>
       </c>
     </row>
     <row r="236">
@@ -16099,14 +16107,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Operating and Other Expenses</t>
-        </is>
-      </c>
+      <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Interest income and other 18</t>
+          <t>Income from equity investments 11</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -16131,10 +16135,10 @@
         </is>
       </c>
       <c r="I236" s="5" t="n">
-        <v>-3.2e-05</v>
+        <v>5e-05</v>
       </c>
       <c r="J236" s="5" t="n">
-        <v>-1.2e-05</v>
+        <v>4.9e-05</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -16155,12 +16159,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Income before Income Taxes</t>
+          <t>Interest expense 18</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -16184,10 +16188,10 @@
         </is>
       </c>
       <c r="I237" s="5" t="n">
-        <v>0.000562</v>
+        <v>0.00022</v>
       </c>
       <c r="J237" s="5" t="n">
-        <v>0.000418</v>
+        <v>0.000388</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
@@ -16203,12 +16207,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Operating and Other Expenses</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Current 16</t>
+          <t>Interest income and other 18</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -16233,10 +16237,10 @@
         </is>
       </c>
       <c r="I238" s="5" t="n">
-        <v>5.3e-05</v>
+        <v>-3.2e-05</v>
       </c>
       <c r="J238" s="5" t="n">
-        <v>4.3e-05</v>
+        <v>-1.2e-05</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
@@ -16252,15 +16256,19 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Operating and Other Expenses</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Deferred 16</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>Income before Income Taxes</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -16282,10 +16290,10 @@
         </is>
       </c>
       <c r="I239" s="5" t="n">
-        <v>6.7e-05</v>
+        <v>0.000562</v>
       </c>
       <c r="J239" s="5" t="n">
-        <v>5.9e-05</v>
+        <v>0.000418</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
@@ -16306,14 +16314,10 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Current 16</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -16335,10 +16339,10 @@
         </is>
       </c>
       <c r="I240" s="5" t="n">
-        <v>0.000442</v>
+        <v>5.3e-05</v>
       </c>
       <c r="J240" s="5" t="n">
-        <v>0.000316</v>
+        <v>4.3e-05</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -16359,7 +16363,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Net Income per Common Share - basic 20</t>
+          <t>Deferred 16</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -16384,10 +16388,10 @@
         </is>
       </c>
       <c r="I241" s="5" t="n">
-        <v>2.13e-06</v>
+        <v>6.7e-05</v>
       </c>
       <c r="J241" s="5" t="n">
-        <v>1.52e-06</v>
+        <v>5.9e-05</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -16408,10 +16412,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Net Income per Common Share - diluted 20</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -16433,10 +16441,10 @@
         </is>
       </c>
       <c r="I242" s="5" t="n">
-        <v>2.13e-06</v>
+        <v>0.000442</v>
       </c>
       <c r="J242" s="5" t="n">
-        <v>1.52e-06</v>
+        <v>0.000316</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -16457,7 +16465,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Common Shares (millions) - basic</t>
+          <t>Net Income per Common Share - basic 20</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -16482,10 +16490,10 @@
         </is>
       </c>
       <c r="I243" s="5" t="n">
-        <v>0.000208</v>
+        <v>2.13e-06</v>
       </c>
       <c r="J243" s="5" t="n">
-        <v>0.000208</v>
+        <v>1.52e-06</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -16506,7 +16514,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Common Shares (millions) - diluted</t>
+          <t>Net Income per Common Share - diluted 20</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -16531,10 +16539,10 @@
         </is>
       </c>
       <c r="I244" s="5" t="n">
-        <v>0.000208</v>
+        <v>2.13e-06</v>
       </c>
       <c r="J244" s="5" t="n">
-        <v>0.000208</v>
+        <v>1.52e-06</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
@@ -16555,14 +16563,10 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Weighted Average Number of Common Shares (millions) - basic</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -16584,10 +16588,10 @@
         </is>
       </c>
       <c r="I245" s="5" t="n">
-        <v>0.000442</v>
+        <v>0.000208</v>
       </c>
       <c r="J245" s="5" t="n">
-        <v>0.000316</v>
+        <v>0.000208</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
@@ -16608,7 +16612,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Foreign currency translation - net investment hedge</t>
+          <t>Weighted Average Number of Common Shares (millions) - diluted</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -16632,13 +16636,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I246" s="5" t="n">
+        <v>0.000208</v>
       </c>
       <c r="J246" s="5" t="n">
-        <v>-6.7e-05</v>
+        <v>0.000208</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -16659,10 +16661,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Foreign currency translation - other</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -16684,10 +16690,10 @@
         </is>
       </c>
       <c r="I247" s="5" t="n">
-        <v>-3e-06</v>
+        <v>0.000442</v>
       </c>
       <c r="J247" s="5" t="n">
-        <v>-9e-06</v>
+        <v>0.000316</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
@@ -16708,7 +16714,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Separation-related pension adjustment</t>
+          <t>Foreign currency translation - net investment hedge</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -16738,7 +16744,7 @@
         </is>
       </c>
       <c r="J248" s="5" t="n">
-        <v>3e-06</v>
+        <v>-6.7e-05</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
@@ -16759,7 +16765,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Changes in pension estimate 21</t>
+          <t>Foreign currency translation - other</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -16783,13 +16789,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I249" s="5" t="n">
+        <v>-3e-06</v>
       </c>
       <c r="J249" s="5" t="n">
-        <v>3e-06</v>
+        <v>-9e-06</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
@@ -16810,7 +16814,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Comprehensive Income</t>
+          <t>Separation-related pension adjustment</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -16834,11 +16838,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I250" s="5" t="n">
-        <v>0.000439</v>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J250" s="5" t="n">
-        <v>0.000246</v>
+        <v>3e-06</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
@@ -16854,19 +16860,15 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Period from incorporation on</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Revenues</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Changes in pension estimate 21</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -16892,10 +16894,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J251" s="5" t="n">
+        <v>3e-06</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
@@ -16911,19 +16911,15 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Period from incorporation on</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Comprehensive Income</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -16944,15 +16940,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I252" s="5" t="n">
+        <v>0.000439</v>
+      </c>
+      <c r="J252" s="5" t="n">
+        <v>0.000246</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
@@ -16973,12 +16965,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Income before income taxes</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -17030,12 +17022,12 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -17087,12 +17079,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t>Income before income taxes</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -17139,26 +17131,38 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Period from incorporation on</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Canadian Natural Gas Pipelines</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" s="5" t="n">
-        <v>4010</v>
-      </c>
-      <c r="F256" s="5" t="n">
-        <v>4469</v>
-      </c>
-      <c r="G256" s="5" t="n">
-        <v>4519</v>
-      </c>
-      <c r="H256" s="5" t="n">
-        <v>4764</v>
+          <t>Income tax expense</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -17184,26 +17188,38 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Period from incorporation on</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>U.S. Natural Gas Pipelines</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" s="5" t="n">
-        <v>4978</v>
-      </c>
-      <c r="F257" s="5" t="n">
-        <v>5031</v>
-      </c>
-      <c r="G257" s="5" t="n">
-        <v>5233</v>
-      </c>
-      <c r="H257" s="5" t="n">
-        <v>5933</v>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -17234,21 +17250,21 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Mexico Natural Gas Pipelines</t>
+          <t>Canadian Natural Gas Pipelines</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
       <c r="E258" s="5" t="n">
-        <v>603</v>
+        <v>4010</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>716</v>
+        <v>4469</v>
       </c>
       <c r="G258" s="5" t="n">
-        <v>605</v>
+        <v>4519</v>
       </c>
       <c r="H258" s="5" t="n">
-        <v>688</v>
+        <v>4764</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -17279,21 +17295,21 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Liquids Pipelines</t>
+          <t>U.S. Natural Gas Pipelines</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" s="5" t="n">
-        <v>2879</v>
+        <v>4978</v>
       </c>
       <c r="F259" s="5" t="n">
-        <v>2371</v>
+        <v>5031</v>
       </c>
       <c r="G259" s="5" t="n">
-        <v>2306</v>
+        <v>5233</v>
       </c>
       <c r="H259" s="5" t="n">
-        <v>2668</v>
+        <v>5933</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
@@ -17324,23 +17340,21 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Power and Energy Solutions</t>
+          <t>Mexico Natural Gas Pipelines</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E260" s="5" t="n">
+        <v>603</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>412</v>
+        <v>716</v>
       </c>
       <c r="G260" s="5" t="n">
-        <v>724</v>
+        <v>605</v>
       </c>
       <c r="H260" s="5" t="n">
-        <v>924</v>
+        <v>688</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -17371,25 +17385,21 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Revenues total</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Liquids Pipelines</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" s="5" t="n">
-        <v>13255</v>
+        <v>2879</v>
       </c>
       <c r="F261" s="5" t="n">
-        <v>12999</v>
+        <v>2371</v>
       </c>
       <c r="G261" s="5" t="n">
-        <v>13387</v>
+        <v>2306</v>
       </c>
       <c r="H261" s="5" t="n">
-        <v>14977</v>
+        <v>2668</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
@@ -17420,7 +17430,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Income from Equity Investments (Note 11)</t>
+          <t>Power and Energy Solutions</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -17430,13 +17440,13 @@
         </is>
       </c>
       <c r="F262" s="5" t="n">
-        <v>1019</v>
+        <v>412</v>
       </c>
       <c r="G262" s="5" t="n">
-        <v>898</v>
+        <v>724</v>
       </c>
       <c r="H262" s="5" t="n">
-        <v>1054</v>
+        <v>924</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
@@ -17467,27 +17477,25 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Impairment of Equity Investment (Notes 7 and 11)</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Revenues total</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="n">
+        <v>13255</v>
+      </c>
+      <c r="F263" s="5" t="n">
+        <v>12999</v>
+      </c>
+      <c r="G263" s="5" t="n">
+        <v>13387</v>
       </c>
       <c r="H263" s="5" t="n">
-        <v>-3048</v>
+        <v>14977</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
@@ -17513,26 +17521,28 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Operating and Other Expenses</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Property taxes</t>
+          <t>Income from Equity Investments (Note 11)</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
-      <c r="E264" s="5" t="n">
-        <v>727</v>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F264" s="5" t="n">
-        <v>727</v>
+        <v>1019</v>
       </c>
       <c r="G264" s="5" t="n">
-        <v>774</v>
+        <v>898</v>
       </c>
       <c r="H264" s="5" t="n">
-        <v>848</v>
+        <v>1054</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
@@ -17558,30 +17568,32 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Operating and Other Expenses</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E265" s="5" t="n">
-        <v>2464</v>
-      </c>
-      <c r="F265" s="5" t="n">
-        <v>2590</v>
-      </c>
-      <c r="G265" s="5" t="n">
-        <v>2522</v>
+          <t>Impairment of Equity Investment (Notes 7 and 11)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H265" s="5" t="n">
-        <v>2584</v>
+        <v>-3048</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -17612,25 +17624,21 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Goodwill and asset impairment charges and other (Notes 6 and 14)</t>
+          <t>Property taxes</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E266" s="5" t="n">
+        <v>727</v>
+      </c>
+      <c r="F266" s="5" t="n">
+        <v>727</v>
       </c>
       <c r="G266" s="5" t="n">
-        <v>2775</v>
+        <v>774</v>
       </c>
       <c r="H266" s="5" t="n">
-        <v>453</v>
+        <v>848</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -17661,25 +17669,25 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Net Gain/(Loss) on Sale of Assets (Note 30)</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation and amortization</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="n">
+        <v>2464</v>
       </c>
       <c r="F267" s="5" t="n">
-        <v>-50</v>
+        <v>2590</v>
       </c>
       <c r="G267" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2522</v>
+      </c>
+      <c r="H267" s="5" t="n">
+        <v>2584</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -17705,32 +17713,30 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Financial Charges</t>
+          <t>Operating and Other Expenses</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Interest expense (Note 20)</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Goodwill and asset impairment charges and other (Notes 6 and 14)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F268" s="5" t="n">
-        <v>2228</v>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>2360</v>
+        <v>2775</v>
       </c>
       <c r="H268" s="5" t="n">
-        <v>2588</v>
+        <v>453</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -17756,26 +17762,30 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Financial Charges</t>
+          <t>Operating and Other Expenses</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Allowance for funds used during construction</t>
+          <t>Net Gain/(Loss) on Sale of Assets (Note 30)</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
-      <c r="E269" s="5" t="n">
-        <v>-475</v>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F269" s="5" t="n">
-        <v>-349</v>
+        <v>-50</v>
       </c>
       <c r="G269" s="5" t="n">
-        <v>-267</v>
-      </c>
-      <c r="H269" s="5" t="n">
-        <v>-369</v>
+        <v>30</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -17806,12 +17816,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Foreign exchange loss/(gain), net (Note 22)</t>
+          <t>Interest expense (Note 20)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -17820,13 +17830,13 @@
         </is>
       </c>
       <c r="F270" s="5" t="n">
-        <v>-28</v>
+        <v>2228</v>
       </c>
       <c r="G270" s="5" t="n">
-        <v>-10</v>
+        <v>2360</v>
       </c>
       <c r="H270" s="5" t="n">
-        <v>185</v>
+        <v>2588</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -17857,21 +17867,21 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Interest income and other</t>
+          <t>Allowance for funds used during construction</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" s="5" t="n">
-        <v>-460</v>
+        <v>-475</v>
       </c>
       <c r="F271" s="5" t="n">
-        <v>-185</v>
+        <v>-349</v>
       </c>
       <c r="G271" s="5" t="n">
-        <v>-190</v>
+        <v>-267</v>
       </c>
       <c r="H271" s="5" t="n">
-        <v>-146</v>
+        <v>-369</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -17897,26 +17907,32 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Income Tax Expense</t>
+          <t>Financial Charges</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" s="5" t="n">
-        <v>699</v>
+          <t>Foreign exchange loss/(gain), net (Note 22)</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F272" s="5" t="n">
-        <v>252</v>
+        <v>-28</v>
       </c>
       <c r="G272" s="5" t="n">
-        <v>305</v>
+        <v>-10</v>
       </c>
       <c r="H272" s="5" t="n">
-        <v>415</v>
+        <v>185</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -17942,26 +17958,26 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Income Tax Expense</t>
+          <t>Financial Charges</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Deferred</t>
+          <t>Interest income and other</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" s="5" t="n">
-        <v>55</v>
+        <v>-460</v>
       </c>
       <c r="F273" s="5" t="n">
-        <v>-58</v>
+        <v>-185</v>
       </c>
       <c r="G273" s="5" t="n">
-        <v>-185</v>
+        <v>-190</v>
       </c>
       <c r="H273" s="5" t="n">
-        <v>174</v>
+        <v>-146</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -17992,21 +18008,21 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Income Tax Expense total</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" s="5" t="n">
-        <v>754</v>
+        <v>699</v>
       </c>
       <c r="F274" s="5" t="n">
-        <v>194</v>
+        <v>252</v>
       </c>
       <c r="G274" s="5" t="n">
-        <v>120</v>
+        <v>305</v>
       </c>
       <c r="H274" s="5" t="n">
-        <v>589</v>
+        <v>415</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -18037,25 +18053,21 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" s="5" t="n">
-        <v>4433</v>
+        <v>55</v>
       </c>
       <c r="F275" s="5" t="n">
-        <v>4913</v>
+        <v>-58</v>
       </c>
       <c r="G275" s="5" t="n">
-        <v>2046</v>
+        <v>-185</v>
       </c>
       <c r="H275" s="5" t="n">
-        <v>785</v>
+        <v>174</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -18086,23 +18098,21 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Net income attributable to non-controlling interests (Note 23)</t>
+          <t>Income Tax Expense total</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E276" s="5" t="n">
+        <v>754</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>297</v>
+        <v>194</v>
       </c>
       <c r="G276" s="5" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="H276" s="5" t="n">
-        <v>37</v>
+        <v>589</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -18133,21 +18143,25 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Net Income Attributable to Controlling Interests</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E277" s="5" t="n">
-        <v>4140</v>
+        <v>4433</v>
       </c>
       <c r="F277" s="5" t="n">
-        <v>4616</v>
+        <v>4913</v>
       </c>
       <c r="G277" s="5" t="n">
-        <v>1955</v>
+        <v>2046</v>
       </c>
       <c r="H277" s="5" t="n">
-        <v>748</v>
+        <v>785</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -18178,21 +18192,23 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Preferred share dividends</t>
+          <t>Net income attributable to non-controlling interests (Note 23)</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
-      <c r="E278" s="5" t="n">
-        <v>164</v>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F278" s="5" t="n">
-        <v>159</v>
+        <v>297</v>
       </c>
       <c r="G278" s="5" t="n">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="H278" s="5" t="n">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -18223,21 +18239,21 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Net Income Attributable to Common Shares</t>
+          <t>Net Income Attributable to Controlling Interests</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
       <c r="E279" s="5" t="n">
-        <v>3976</v>
+        <v>4140</v>
       </c>
       <c r="F279" s="5" t="n">
-        <v>4457</v>
+        <v>4616</v>
       </c>
       <c r="G279" s="5" t="n">
-        <v>1815</v>
+        <v>1955</v>
       </c>
       <c r="H279" s="5" t="n">
-        <v>641</v>
+        <v>748</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -18263,30 +18279,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Net Income per Common Share</t>
+          <t>Income Tax Expense</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Preferred share dividends</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" s="5" t="n">
-        <v>4.280000000000001e-06</v>
+        <v>164</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>4.74e-06</v>
+        <v>159</v>
       </c>
       <c r="G280" s="5" t="n">
-        <v>1.87e-06</v>
+        <v>140</v>
       </c>
       <c r="H280" s="5" t="n">
-        <v>6.4e-07</v>
+        <v>107</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -18312,30 +18324,26 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Net Income per Common Share</t>
+          <t>Income Tax Expense</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Diluted</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Net Income Attributable to Common Shares</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" s="5" t="n">
-        <v>4.27e-06</v>
+        <v>3976</v>
       </c>
       <c r="F281" s="5" t="n">
-        <v>4.74e-06</v>
+        <v>4457</v>
       </c>
       <c r="G281" s="5" t="n">
-        <v>1.86e-06</v>
+        <v>1815</v>
       </c>
       <c r="H281" s="5" t="n">
-        <v>6.4e-07</v>
+        <v>641</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -18366,21 +18374,25 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Dividends Declared per Common Share</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E282" s="5" t="n">
-        <v>3e-06</v>
+        <v>4.280000000000001e-06</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>3.24e-06</v>
+        <v>4.74e-06</v>
       </c>
       <c r="G282" s="5" t="n">
-        <v>3.48e-06</v>
+        <v>1.87e-06</v>
       </c>
       <c r="H282" s="5" t="n">
-        <v>3.6e-06</v>
+        <v>6.4e-07</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -18406,28 +18418,30 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Net Income per Common Share</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Power and Storage</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E283" s="5" t="n">
-        <v>785</v>
+        <v>4.27e-06</v>
       </c>
       <c r="F283" s="5" t="n">
-        <v>412</v>
+        <v>4.74e-06</v>
       </c>
       <c r="G283" s="5" t="n">
-        <v>724</v>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.86e-06</v>
+      </c>
+      <c r="H283" s="5" t="n">
+        <v>6.4e-07</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -18453,28 +18467,26 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Net Income per Common Share</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Income from Equity Investments (Note 10)</t>
+          <t>Dividends Declared per Common Share</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
       <c r="E284" s="5" t="n">
-        <v>920</v>
+        <v>3e-06</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>1019</v>
+        <v>3.24e-06</v>
       </c>
       <c r="G284" s="5" t="n">
-        <v>898</v>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.48e-06</v>
+      </c>
+      <c r="H284" s="5" t="n">
+        <v>3.6e-06</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -18500,27 +18512,23 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Operating and Other Expenses</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Asset impairment charge and other (Note 6)</t>
+          <t>Power and Storage</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E285" s="5" t="n">
+        <v>785</v>
+      </c>
+      <c r="F285" s="5" t="n">
+        <v>412</v>
       </c>
       <c r="G285" s="5" t="n">
-        <v>2775</v>
+        <v>724</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -18551,23 +18559,23 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Operating and Other Expenses</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Net Gain/(Loss) on Assets Sold/Held for Sale (Note 28)</t>
+          <t>Income from Equity Investments (Note 10)</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
       <c r="E286" s="5" t="n">
-        <v>-121</v>
+        <v>920</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>-50</v>
+        <v>1019</v>
       </c>
       <c r="G286" s="5" t="n">
-        <v>30</v>
+        <v>898</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -18598,27 +18606,27 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Financial Charges</t>
+          <t>Operating and Other Expenses</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Interest expense (Note 19)</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
-      <c r="E287" s="5" t="n">
-        <v>2333</v>
-      </c>
-      <c r="F287" s="5" t="n">
-        <v>2228</v>
+          <t>Asset impairment charge and other (Note 6)</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>2360</v>
+        <v>2775</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -18649,40 +18657,138 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Income Tax Expense</t>
+          <t>Operating and Other Expenses</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Net income attributable to non-controlling interests (Note 21)</t>
+          <t>Net Gain/(Loss) on Assets Sold/Held for Sale (Note 28)</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
       <c r="E288" s="5" t="n">
+        <v>-121</v>
+      </c>
+      <c r="F288" s="5" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G288" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Financial Charges</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Interest expense (Note 19)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="F289" s="5" t="n">
+        <v>2228</v>
+      </c>
+      <c r="G289" s="5" t="n">
+        <v>2360</v>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Income Tax Expense</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Net income attributable to non-controlling interests (Note 21)</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="F288" s="5" t="n">
+      <c r="F290" s="5" t="n">
         <v>297</v>
       </c>
-      <c r="G288" s="5" t="n">
+      <c r="G290" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr">
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
